--- a/public/Ananbay_FBA_template.xlsx
+++ b/public/Ananbay_FBA_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vscode\teb-express\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ManhPineapple\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57424CA4-CEC4-4A05-822D-86560833F502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD55924-93A7-4991-86B3-B153493C0F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>Order ID</t>
   </si>
@@ -159,6 +159,9 @@
       </rPr>
       <t xml:space="preserve"> Rio Vista Avenue</t>
     </r>
+  </si>
+  <si>
+    <t>FFBA</t>
   </si>
 </sst>
 </file>
@@ -676,7 +679,7 @@
         <v>20</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="15.6" customHeight="1">
@@ -729,8 +732,8 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{473ABFE3-B36F-4E6D-B686-F0904B700F0C}">
-      <formula1>"FBA"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576" xr:uid="{5349DC19-E50D-4850-8CA0-1F33CCB308CD}">
+      <formula1>"FBA, FFBA"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
